--- a/sets.xlsx
+++ b/sets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ce3gk\OneDrive\Escritorio\opti\proyecto\ics1113_proyecto_grupo03\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Documentos\UC\Semester 6\OPTI\tarea\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4F063F-FAC4-4711-BA90-D80EF9669EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB36AEF-1AFC-4C53-8971-C79482401242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SETS" sheetId="1" r:id="rId1"/>
@@ -450,9 +450,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H366"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -481,7 +481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -495,7 +495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2028</v>
       </c>
@@ -506,7 +506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>2029</v>
       </c>
@@ -517,7 +517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>2030</v>
       </c>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2031</v>
       </c>
@@ -539,7 +539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>2032</v>
       </c>
@@ -550,7 +550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>2033</v>
       </c>
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>2034</v>
       </c>
@@ -572,7 +572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>2035</v>
       </c>
@@ -584,7 +584,7 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>2036</v>
       </c>
@@ -595,7 +595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>2037</v>
       </c>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>2038</v>
       </c>
@@ -617,7 +617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>2039</v>
       </c>
@@ -628,7 +628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>2040</v>
       </c>
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>2041</v>
       </c>
@@ -650,7 +650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>2042</v>
       </c>
@@ -661,7 +661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>2043</v>
       </c>
@@ -672,7 +672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>2044</v>
       </c>
@@ -683,7 +683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>2045</v>
       </c>
@@ -694,7 +694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C22">
         <v>21</v>
       </c>
@@ -702,7 +702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C23">
         <v>22</v>
       </c>
@@ -710,7 +710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C24">
         <v>23</v>
       </c>
@@ -718,1712 +718,1712 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C354">
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C355">
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C356">
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C357">
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C358">
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C359">
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C360">
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C361">
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C362">
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C363">
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C364">
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C365">
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C366">
         <v>365</v>
       </c>
@@ -2436,9 +2436,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F41BF85-7983-4005-A8A4-1DDFC79BAD5F}">
   <dimension ref="A1:D366"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2478,10 +2478,10 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2028</v>
       </c>
@@ -2489,10 +2489,10 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>2029</v>
       </c>
@@ -2500,10 +2500,10 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>2030</v>
       </c>
@@ -2511,10 +2511,10 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2031</v>
       </c>
@@ -2522,10 +2522,10 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>2032</v>
       </c>
@@ -2533,10 +2533,10 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>2033</v>
       </c>
@@ -2544,10 +2544,10 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>2034</v>
       </c>
@@ -2555,10 +2555,10 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>2035</v>
       </c>
@@ -2566,10 +2566,10 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>2036</v>
       </c>
@@ -2577,1811 +2577,1814 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C19">
         <v>18</v>
       </c>
       <c r="D19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C20">
         <v>19</v>
       </c>
       <c r="D20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>20</v>
       </c>
       <c r="D21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C22">
         <v>21</v>
       </c>
       <c r="D22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C354">
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C355">
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C356">
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C357">
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C358">
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C359">
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C360">
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C361">
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C362">
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C363">
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C364">
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C365">
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C366">
         <v>365</v>
       </c>
